--- a/data/trans_orig/IP31KM02_R_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_R_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8967</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5008</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14151</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12991</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7248</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21294</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51296</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46112</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55255</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>58409</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50106</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64152</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62678</t>
+          <t>46316</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55361</t>
+          <t>41625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67765</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>121086</t>
+          <t>97614</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109492</t>
+          <t>90968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129372</t>
+          <t>103096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57944</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>46929</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68516</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>50,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53620</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>71868</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>42,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>57,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63950</t>
+          <t>51233</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52149</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75122</t>
+          <t>60278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>117570</t>
+          <t>109176</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82012</t>
+          <t>94690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138413</t>
+          <t>123136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57007</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46435</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>68022</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>49,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>72029</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53781</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>102472</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>57,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62473</t>
+          <t>48100</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51301</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74274</t>
+          <t>56900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>134501</t>
+          <t>105108</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113658</t>
+          <t>91148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170059</t>
+          <t>119594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33464</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27772</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39763</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28678</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22956</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34702</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43443</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>66105</t>
+          <t>60911</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56825</t>
+          <t>52631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74720</t>
+          <t>69037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23835</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17536</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29527</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26874</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20850</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32596</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>48,38%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>58,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27206</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34407</t>
+          <t>32537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>50500</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45465</t>
+          <t>42374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63360</t>
+          <t>58780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51969</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42197</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59469</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>51527</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43930</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57501</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>73,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>63,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56902</t>
+          <t>52496</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47075</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65529</t>
+          <t>58754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>108429</t>
+          <t>104465</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96566</t>
+          <t>91999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119002</t>
+          <t>114083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17847</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27619</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>18155</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12181</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25752</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28292</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36620</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48483</t>
+          <t>48279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33333</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31085</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>34566</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32054</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>136</t>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>74145</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71625</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3165</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22930</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17964</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>28285</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>48,57%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17156</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>12626</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>22522</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32595</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>43538</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36182</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51168</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24279</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>18924</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>29245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>51,43%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>61,95%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>27134</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>21768</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>31664</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>71,49%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>27214</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>54534</t>
+          <t>51493</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61890</t>
+          <t>58531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,97%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>99553</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>86128</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>109226</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>61,27%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>77,7%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>96942</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>88982</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>104548</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>78,37%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>71,94%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>84,52%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>113407</t>
+          <t>93318</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100834</t>
+          <t>84777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123780</t>
+          <t>101263</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>210350</t>
+          <t>192872</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193480</t>
+          <t>177243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223748</t>
+          <t>205790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>41018</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>31345</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>54443</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>38,73%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>26754</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>19148</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34714</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41637</t>
+          <t>28504</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>68390</t>
+          <t>69522</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54992</t>
+          <t>56604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85260</t>
+          <t>85151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>144598</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>136991</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>149708</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>92,02%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>87,18%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>109769</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>100624</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>115737</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>141770</t>
+          <t>116455</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134532</t>
+          <t>106156</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146358</t>
+          <t>124536</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>251539</t>
+          <t>261053</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>240263</t>
+          <t>248299</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259826</t>
+          <t>270785</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12538</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7428</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>20145</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>18896</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12928</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>28041</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>33983</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>24251</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>46737</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>459003</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>435647</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>481165</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>66,83%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>63,43%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>70,06%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>404017</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>349862</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>434069</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>53,57%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>401193</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>462686</t>
+          <t>380651</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>516775</t>
+          <t>420442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>896504</t>
+          <t>860195</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>839638</t>
+          <t>828113</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>934115</t>
+          <t>890164</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>227821</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>205659</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>251177</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>33,17%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>249117</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>219065</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>303272</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>252246</t>
+          <t>217015</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>227958</t>
+          <t>197766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>237557</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>501363</t>
+          <t>444836</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>463752</t>
+          <t>414867</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>558229</t>
+          <t>476918</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
